--- a/Data/EXCEL/Transfer/salemon/202512/7806-salemon-202512.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202512/7806-salemon-202512.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\202512\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202512\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{740DBC99-B2EF-452C-8A50-8B58967A6591}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1ADC610-8544-4F4A-A4C2-D60163B7F3BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="930" windowWidth="26910" windowHeight="18975" xr2:uid="{B4823936-AFD4-4BC2-A4C5-E47A82AC43D9}"/>
+    <workbookView xWindow="0" yWindow="1740" windowWidth="17565" windowHeight="11295" xr2:uid="{2136D3F5-5FF0-4726-A4A6-6C03CF635683}"/>
   </bookViews>
   <sheets>
     <sheet name="7806-salemon-202512" sheetId="2" r:id="rId1"/>
@@ -854,16 +854,16 @@
     <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1258,20 +1258,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F1B3AF3-75B8-4BC3-8678-1BA52F62E04A}">
-  <dimension ref="A1:Q17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC8A4D78-2CD1-4706-B1D8-5FDC0B247799}">
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.125" customWidth="1"/>
-    <col min="2" max="7" width="12.125" customWidth="1"/>
-    <col min="8" max="9" width="12.75" customWidth="1"/>
-    <col min="10" max="10" width="12.125" customWidth="1"/>
-    <col min="11" max="11" width="12.75" customWidth="1"/>
-    <col min="12" max="12" width="12.125" customWidth="1"/>
-    <col min="13" max="14" width="12.75" customWidth="1"/>
-    <col min="15" max="15" width="12.125" customWidth="1"/>
-    <col min="16" max="16" width="12.75" customWidth="1"/>
-    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="1" max="1" width="9.375" customWidth="1"/>
+    <col min="2" max="6" width="7.5" customWidth="1"/>
+    <col min="7" max="9" width="7.875" customWidth="1"/>
+    <col min="10" max="10" width="7.5" customWidth="1"/>
+    <col min="11" max="11" width="7.875" customWidth="1"/>
+    <col min="12" max="12" width="7.5" customWidth="1"/>
+    <col min="13" max="14" width="7.875" customWidth="1"/>
+    <col min="15" max="15" width="7.5" customWidth="1"/>
+    <col min="16" max="16" width="7.875" customWidth="1"/>
+    <col min="17" max="17" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -1424,690 +1424,743 @@
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B5" s="6">
-        <v>63.9</v>
+        <v>64</v>
       </c>
       <c r="C5" s="6">
-        <v>64</v>
+        <v>74.3</v>
       </c>
       <c r="D5" s="6">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="E5" s="6">
-        <v>59.5</v>
+        <v>63.1</v>
       </c>
       <c r="F5" s="7">
-        <v>0.1</v>
+        <v>10.3</v>
       </c>
       <c r="G5" s="7">
-        <v>0.16</v>
+        <v>16.09</v>
       </c>
       <c r="H5" s="8">
-        <v>0.47799999999999998</v>
+        <v>0.49099999999999999</v>
       </c>
       <c r="I5" s="7">
-        <v>21.8</v>
+        <v>2.86</v>
       </c>
       <c r="J5" s="7">
-        <v>29.1</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="K5" s="8">
-        <v>4.9000000000000004</v>
+        <v>5.39</v>
       </c>
       <c r="L5" s="7">
-        <v>24.5</v>
+        <v>23.8</v>
       </c>
       <c r="M5" s="8">
-        <v>0.47799999999999998</v>
+        <v>0.49099999999999999</v>
       </c>
       <c r="N5" s="7">
-        <v>21.8</v>
+        <v>2.86</v>
       </c>
       <c r="O5" s="7">
-        <v>29.1</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="P5" s="8">
-        <v>4.9000000000000004</v>
+        <v>5.39</v>
       </c>
       <c r="Q5" s="7">
-        <v>24.5</v>
+        <v>23.8</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B6" s="11">
-        <v>67.3</v>
+        <v>63.9</v>
       </c>
       <c r="C6" s="11">
-        <v>63.9</v>
+        <v>64</v>
       </c>
       <c r="D6" s="11">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E6" s="11">
-        <v>61.3</v>
+        <v>59.5</v>
       </c>
       <c r="F6" s="12">
-        <v>-3.4</v>
+        <v>0.1</v>
       </c>
       <c r="G6" s="12">
-        <v>-5.05</v>
+        <v>0.16</v>
       </c>
       <c r="H6" s="13">
-        <v>0.39200000000000002</v>
-      </c>
-      <c r="I6" s="14">
-        <v>16.3</v>
-      </c>
-      <c r="J6" s="14">
-        <v>14.3</v>
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="I6" s="12">
+        <v>21.8</v>
+      </c>
+      <c r="J6" s="12">
+        <v>29.1</v>
       </c>
       <c r="K6" s="13">
-        <v>4.42</v>
-      </c>
-      <c r="L6" s="14">
-        <v>24.1</v>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="L6" s="12">
+        <v>24.5</v>
       </c>
       <c r="M6" s="13">
-        <v>0.39200000000000002</v>
-      </c>
-      <c r="N6" s="14">
-        <v>16.3</v>
-      </c>
-      <c r="O6" s="14">
-        <v>14.3</v>
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="N6" s="12">
+        <v>21.8</v>
+      </c>
+      <c r="O6" s="12">
+        <v>29.1</v>
       </c>
       <c r="P6" s="13">
-        <v>4.42</v>
-      </c>
-      <c r="Q6" s="14">
-        <v>24.1</v>
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>24.5</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B7" s="6">
-        <v>68</v>
+        <v>67.3</v>
       </c>
       <c r="C7" s="6">
-        <v>67.3</v>
+        <v>63.9</v>
       </c>
       <c r="D7" s="6">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E7" s="6">
-        <v>64.3</v>
-      </c>
-      <c r="F7" s="15">
-        <v>-0.7</v>
-      </c>
-      <c r="G7" s="15">
-        <v>-1.03</v>
+        <v>61.3</v>
+      </c>
+      <c r="F7" s="14">
+        <v>-3.4</v>
+      </c>
+      <c r="G7" s="14">
+        <v>-5.05</v>
       </c>
       <c r="H7" s="8">
-        <v>0.33700000000000002</v>
-      </c>
-      <c r="I7" s="15">
-        <v>-32.5</v>
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="I7" s="7">
+        <v>16.3</v>
       </c>
       <c r="J7" s="7">
-        <v>4.34</v>
+        <v>14.3</v>
       </c>
       <c r="K7" s="8">
-        <v>4.03</v>
+        <v>4.42</v>
       </c>
       <c r="L7" s="7">
-        <v>25.1</v>
+        <v>24.1</v>
       </c>
       <c r="M7" s="8">
-        <v>0.33700000000000002</v>
-      </c>
-      <c r="N7" s="15">
-        <v>-32.5</v>
+        <v>0.39200000000000002</v>
+      </c>
+      <c r="N7" s="7">
+        <v>16.3</v>
       </c>
       <c r="O7" s="7">
-        <v>4.34</v>
+        <v>14.3</v>
       </c>
       <c r="P7" s="8">
-        <v>4.03</v>
+        <v>4.42</v>
       </c>
       <c r="Q7" s="7">
-        <v>25.1</v>
+        <v>24.1</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B8" s="11">
-        <v>70.5</v>
+        <v>68</v>
       </c>
       <c r="C8" s="11">
-        <v>68</v>
+        <v>67.3</v>
       </c>
       <c r="D8" s="11">
-        <v>74.2</v>
+        <v>71</v>
       </c>
       <c r="E8" s="11">
-        <v>65.900000000000006</v>
-      </c>
-      <c r="F8" s="12">
-        <v>-2.5</v>
-      </c>
-      <c r="G8" s="12">
-        <v>-3.55</v>
+        <v>64.3</v>
+      </c>
+      <c r="F8" s="15">
+        <v>-0.7</v>
+      </c>
+      <c r="G8" s="15">
+        <v>-1.03</v>
       </c>
       <c r="H8" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="I8" s="14">
-        <v>44.2</v>
-      </c>
-      <c r="J8" s="14">
-        <v>36.700000000000003</v>
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="I8" s="15">
+        <v>-32.5</v>
+      </c>
+      <c r="J8" s="12">
+        <v>4.34</v>
       </c>
       <c r="K8" s="13">
-        <v>3.69</v>
-      </c>
-      <c r="L8" s="14">
-        <v>27.4</v>
+        <v>4.03</v>
+      </c>
+      <c r="L8" s="12">
+        <v>25.1</v>
       </c>
       <c r="M8" s="13">
-        <v>0.5</v>
-      </c>
-      <c r="N8" s="14">
-        <v>44.2</v>
-      </c>
-      <c r="O8" s="14">
-        <v>36.700000000000003</v>
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="N8" s="15">
+        <v>-32.5</v>
+      </c>
+      <c r="O8" s="12">
+        <v>4.34</v>
       </c>
       <c r="P8" s="13">
-        <v>3.69</v>
-      </c>
-      <c r="Q8" s="14">
-        <v>27.4</v>
+        <v>4.03</v>
+      </c>
+      <c r="Q8" s="12">
+        <v>25.1</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B9" s="6">
-        <v>64.3</v>
+        <v>70.5</v>
       </c>
       <c r="C9" s="6">
-        <v>70.5</v>
+        <v>68</v>
       </c>
       <c r="D9" s="6">
-        <v>71</v>
+        <v>74.2</v>
       </c>
       <c r="E9" s="6">
-        <v>63.2</v>
-      </c>
-      <c r="F9" s="7">
-        <v>6.2</v>
-      </c>
-      <c r="G9" s="7">
-        <v>9.64</v>
+        <v>65.900000000000006</v>
+      </c>
+      <c r="F9" s="14">
+        <v>-2.5</v>
+      </c>
+      <c r="G9" s="14">
+        <v>-3.55</v>
       </c>
       <c r="H9" s="8">
-        <v>0.34599999999999997</v>
-      </c>
-      <c r="I9" s="15">
-        <v>-19.5</v>
-      </c>
-      <c r="J9" s="15">
-        <v>-17.8</v>
+        <v>0.5</v>
+      </c>
+      <c r="I9" s="7">
+        <v>44.2</v>
+      </c>
+      <c r="J9" s="7">
+        <v>36.700000000000003</v>
       </c>
       <c r="K9" s="8">
-        <v>3.19</v>
+        <v>3.69</v>
       </c>
       <c r="L9" s="7">
-        <v>26.1</v>
+        <v>27.4</v>
       </c>
       <c r="M9" s="8">
-        <v>0.34599999999999997</v>
-      </c>
-      <c r="N9" s="15">
-        <v>-19.5</v>
-      </c>
-      <c r="O9" s="15">
-        <v>-17.8</v>
+        <v>0.5</v>
+      </c>
+      <c r="N9" s="7">
+        <v>44.2</v>
+      </c>
+      <c r="O9" s="7">
+        <v>36.700000000000003</v>
       </c>
       <c r="P9" s="8">
-        <v>3.19</v>
+        <v>3.69</v>
       </c>
       <c r="Q9" s="7">
-        <v>26.1</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B10" s="11">
-        <v>66</v>
+        <v>64.3</v>
       </c>
       <c r="C10" s="11">
-        <v>64.3</v>
+        <v>70.5</v>
       </c>
       <c r="D10" s="11">
-        <v>67.3</v>
+        <v>71</v>
       </c>
       <c r="E10" s="11">
-        <v>61</v>
+        <v>63.2</v>
       </c>
       <c r="F10" s="12">
-        <v>-1.7</v>
+        <v>6.2</v>
       </c>
       <c r="G10" s="12">
-        <v>-2.58</v>
+        <v>9.64</v>
       </c>
       <c r="H10" s="13">
-        <v>0.43</v>
-      </c>
-      <c r="I10" s="12">
-        <v>-11.7</v>
-      </c>
-      <c r="J10" s="14">
-        <v>62.3</v>
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="I10" s="15">
+        <v>-19.5</v>
+      </c>
+      <c r="J10" s="15">
+        <v>-17.8</v>
       </c>
       <c r="K10" s="13">
-        <v>2.84</v>
-      </c>
-      <c r="L10" s="14">
-        <v>34.799999999999997</v>
+        <v>3.19</v>
+      </c>
+      <c r="L10" s="12">
+        <v>26.1</v>
       </c>
       <c r="M10" s="13">
-        <v>0.43</v>
-      </c>
-      <c r="N10" s="12">
-        <v>-11.7</v>
-      </c>
-      <c r="O10" s="14">
-        <v>62.3</v>
+        <v>0.34599999999999997</v>
+      </c>
+      <c r="N10" s="15">
+        <v>-19.5</v>
+      </c>
+      <c r="O10" s="15">
+        <v>-17.8</v>
       </c>
       <c r="P10" s="13">
-        <v>2.84</v>
-      </c>
-      <c r="Q10" s="14">
-        <v>34.799999999999997</v>
+        <v>3.19</v>
+      </c>
+      <c r="Q10" s="12">
+        <v>26.1</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B11" s="6">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C11" s="6">
-        <v>66</v>
+        <v>64.3</v>
       </c>
       <c r="D11" s="6">
-        <v>70.5</v>
+        <v>67.3</v>
       </c>
       <c r="E11" s="6">
-        <v>66</v>
-      </c>
-      <c r="F11" s="15">
-        <v>-3</v>
-      </c>
-      <c r="G11" s="15">
-        <v>-4.3499999999999996</v>
+        <v>61</v>
+      </c>
+      <c r="F11" s="14">
+        <v>-1.7</v>
+      </c>
+      <c r="G11" s="14">
+        <v>-2.58</v>
       </c>
       <c r="H11" s="8">
-        <v>0.48699999999999999</v>
-      </c>
-      <c r="I11" s="7">
-        <v>12</v>
+        <v>0.43</v>
+      </c>
+      <c r="I11" s="14">
+        <v>-11.7</v>
       </c>
       <c r="J11" s="7">
-        <v>33.200000000000003</v>
+        <v>62.3</v>
       </c>
       <c r="K11" s="8">
-        <v>2.41</v>
+        <v>2.84</v>
       </c>
       <c r="L11" s="7">
-        <v>30.9</v>
+        <v>34.799999999999997</v>
       </c>
       <c r="M11" s="8">
-        <v>0.48699999999999999</v>
-      </c>
-      <c r="N11" s="7">
-        <v>12</v>
+        <v>0.43</v>
+      </c>
+      <c r="N11" s="14">
+        <v>-11.7</v>
       </c>
       <c r="O11" s="7">
-        <v>33.200000000000003</v>
+        <v>62.3</v>
       </c>
       <c r="P11" s="8">
-        <v>2.41</v>
+        <v>2.84</v>
       </c>
       <c r="Q11" s="7">
-        <v>30.9</v>
+        <v>34.799999999999997</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B12" s="11">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" s="11">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D12" s="11">
-        <v>75.5</v>
+        <v>70.5</v>
       </c>
       <c r="E12" s="11">
-        <v>62.7</v>
-      </c>
-      <c r="F12" s="14">
-        <v>1</v>
-      </c>
-      <c r="G12" s="14">
-        <v>1.47</v>
+        <v>66</v>
+      </c>
+      <c r="F12" s="15">
+        <v>-3</v>
+      </c>
+      <c r="G12" s="15">
+        <v>-4.3499999999999996</v>
       </c>
       <c r="H12" s="13">
-        <v>0.435</v>
+        <v>0.48699999999999999</v>
       </c>
       <c r="I12" s="12">
-        <v>-44.3</v>
-      </c>
-      <c r="J12" s="14">
-        <v>39.200000000000003</v>
+        <v>12</v>
+      </c>
+      <c r="J12" s="12">
+        <v>33.200000000000003</v>
       </c>
       <c r="K12" s="13">
-        <v>1.92</v>
-      </c>
-      <c r="L12" s="14">
-        <v>30.3</v>
+        <v>2.41</v>
+      </c>
+      <c r="L12" s="12">
+        <v>30.9</v>
       </c>
       <c r="M12" s="13">
-        <v>0.435</v>
+        <v>0.48699999999999999</v>
       </c>
       <c r="N12" s="12">
-        <v>-44.3</v>
-      </c>
-      <c r="O12" s="14">
-        <v>39.200000000000003</v>
+        <v>12</v>
+      </c>
+      <c r="O12" s="12">
+        <v>33.200000000000003</v>
       </c>
       <c r="P12" s="13">
-        <v>1.92</v>
-      </c>
-      <c r="Q12" s="14">
-        <v>30.3</v>
+        <v>2.41</v>
+      </c>
+      <c r="Q12" s="12">
+        <v>30.9</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B13" s="6">
-        <v>70.5</v>
+        <v>68</v>
       </c>
       <c r="C13" s="6">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D13" s="6">
-        <v>80.5</v>
+        <v>75.5</v>
       </c>
       <c r="E13" s="6">
-        <v>66</v>
-      </c>
-      <c r="F13" s="15">
-        <v>-2.5</v>
-      </c>
-      <c r="G13" s="15">
-        <v>-3.55</v>
+        <v>62.7</v>
+      </c>
+      <c r="F13" s="7">
+        <v>1</v>
+      </c>
+      <c r="G13" s="7">
+        <v>1.47</v>
       </c>
       <c r="H13" s="8">
-        <v>0.78100000000000003</v>
-      </c>
-      <c r="I13" s="7">
-        <v>112.5</v>
+        <v>0.435</v>
+      </c>
+      <c r="I13" s="14">
+        <v>-44.3</v>
       </c>
       <c r="J13" s="7">
-        <v>56.8</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="K13" s="8">
-        <v>1.49</v>
+        <v>1.92</v>
       </c>
       <c r="L13" s="7">
-        <v>27.9</v>
+        <v>30.3</v>
       </c>
       <c r="M13" s="8">
-        <v>0.78100000000000003</v>
-      </c>
-      <c r="N13" s="7">
-        <v>112.5</v>
+        <v>0.435</v>
+      </c>
+      <c r="N13" s="14">
+        <v>-44.3</v>
       </c>
       <c r="O13" s="7">
-        <v>56.8</v>
+        <v>39.200000000000003</v>
       </c>
       <c r="P13" s="8">
-        <v>1.49</v>
+        <v>1.92</v>
       </c>
       <c r="Q13" s="7">
-        <v>27.9</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B14" s="11">
-        <v>74</v>
+        <v>70.5</v>
       </c>
       <c r="C14" s="11">
-        <v>70.5</v>
+        <v>68</v>
       </c>
       <c r="D14" s="11">
-        <v>75.5</v>
+        <v>80.5</v>
       </c>
       <c r="E14" s="11">
-        <v>69</v>
-      </c>
-      <c r="F14" s="12">
-        <v>-3.5</v>
-      </c>
-      <c r="G14" s="12">
-        <v>-4.7300000000000004</v>
+        <v>66</v>
+      </c>
+      <c r="F14" s="15">
+        <v>-2.5</v>
+      </c>
+      <c r="G14" s="15">
+        <v>-3.55</v>
       </c>
       <c r="H14" s="13">
-        <v>0.36699999999999999</v>
-      </c>
-      <c r="I14" s="14">
-        <v>7.63</v>
-      </c>
-      <c r="J14" s="14">
-        <v>49.1</v>
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="I14" s="12">
+        <v>112.5</v>
+      </c>
+      <c r="J14" s="12">
+        <v>56.8</v>
       </c>
       <c r="K14" s="13">
-        <v>0.70899999999999996</v>
-      </c>
-      <c r="L14" s="14">
-        <v>6.33</v>
+        <v>1.49</v>
+      </c>
+      <c r="L14" s="12">
+        <v>27.9</v>
       </c>
       <c r="M14" s="13">
-        <v>0.36699999999999999</v>
-      </c>
-      <c r="N14" s="14">
-        <v>7.63</v>
-      </c>
-      <c r="O14" s="14">
-        <v>49.1</v>
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="N14" s="12">
+        <v>112.5</v>
+      </c>
+      <c r="O14" s="12">
+        <v>56.8</v>
       </c>
       <c r="P14" s="13">
-        <v>0.70899999999999996</v>
-      </c>
-      <c r="Q14" s="14">
-        <v>6.33</v>
+        <v>1.49</v>
+      </c>
+      <c r="Q14" s="12">
+        <v>27.9</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B15" s="6">
-        <v>74.5</v>
+        <v>74</v>
       </c>
       <c r="C15" s="6">
-        <v>74</v>
+        <v>70.5</v>
       </c>
       <c r="D15" s="6">
-        <v>76.3</v>
+        <v>75.5</v>
       </c>
       <c r="E15" s="6">
-        <v>63.7</v>
-      </c>
-      <c r="F15" s="15">
-        <v>-0.5</v>
-      </c>
-      <c r="G15" s="15">
-        <v>-0.67</v>
+        <v>69</v>
+      </c>
+      <c r="F15" s="14">
+        <v>-3.5</v>
+      </c>
+      <c r="G15" s="14">
+        <v>-4.7300000000000004</v>
       </c>
       <c r="H15" s="8">
-        <v>0.34100000000000003</v>
-      </c>
-      <c r="I15" s="15">
-        <v>-18.8</v>
-      </c>
-      <c r="J15" s="15">
-        <v>-18.8</v>
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="I15" s="7">
+        <v>7.63</v>
+      </c>
+      <c r="J15" s="7">
+        <v>49.1</v>
       </c>
       <c r="K15" s="8">
-        <v>0.34100000000000003</v>
-      </c>
-      <c r="L15" s="15">
-        <v>-18.8</v>
+        <v>0.70899999999999996</v>
+      </c>
+      <c r="L15" s="7">
+        <v>6.33</v>
       </c>
       <c r="M15" s="8">
-        <v>0.34100000000000003</v>
-      </c>
-      <c r="N15" s="15">
-        <v>-18.8</v>
-      </c>
-      <c r="O15" s="15">
-        <v>-18.8</v>
+        <v>0.36699999999999999</v>
+      </c>
+      <c r="N15" s="7">
+        <v>7.63</v>
+      </c>
+      <c r="O15" s="7">
+        <v>49.1</v>
       </c>
       <c r="P15" s="8">
-        <v>0.34100000000000003</v>
-      </c>
-      <c r="Q15" s="15">
-        <v>-18.8</v>
+        <v>0.70899999999999996</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>6.33</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
-        <v>45627</v>
+        <v>45658</v>
       </c>
       <c r="B16" s="11">
-        <v>73.5</v>
+        <v>74.5</v>
       </c>
       <c r="C16" s="11">
-        <v>74.5</v>
+        <v>74</v>
       </c>
       <c r="D16" s="11">
-        <v>90</v>
+        <v>76.3</v>
       </c>
       <c r="E16" s="11">
-        <v>68.5</v>
-      </c>
-      <c r="F16" s="14">
-        <v>1</v>
-      </c>
-      <c r="G16" s="14">
-        <v>1.36</v>
+        <v>63.7</v>
+      </c>
+      <c r="F16" s="15">
+        <v>-0.5</v>
+      </c>
+      <c r="G16" s="15">
+        <v>-0.67</v>
       </c>
       <c r="H16" s="13">
-        <v>0.42</v>
-      </c>
-      <c r="I16" s="14">
-        <v>13.6</v>
-      </c>
-      <c r="J16" s="14">
-        <v>26.1</v>
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="I16" s="15">
+        <v>-18.8</v>
+      </c>
+      <c r="J16" s="15">
+        <v>-18.8</v>
       </c>
       <c r="K16" s="13">
-        <v>4.3499999999999996</v>
-      </c>
-      <c r="L16" s="14">
-        <v>7.81</v>
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-18.8</v>
       </c>
       <c r="M16" s="13">
-        <v>0.42</v>
-      </c>
-      <c r="N16" s="14">
-        <v>13.6</v>
-      </c>
-      <c r="O16" s="14">
-        <v>26.1</v>
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-18.8</v>
+      </c>
+      <c r="O16" s="15">
+        <v>-18.8</v>
       </c>
       <c r="P16" s="13">
-        <v>4.3499999999999996</v>
-      </c>
-      <c r="Q16" s="14">
-        <v>7.81</v>
+        <v>0.34100000000000003</v>
+      </c>
+      <c r="Q16" s="15">
+        <v>-18.8</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
+        <v>45627</v>
+      </c>
+      <c r="B17" s="6">
+        <v>73.5</v>
+      </c>
+      <c r="C17" s="6">
+        <v>74.5</v>
+      </c>
+      <c r="D17" s="6">
+        <v>90</v>
+      </c>
+      <c r="E17" s="6">
+        <v>68.5</v>
+      </c>
+      <c r="F17" s="7">
+        <v>1</v>
+      </c>
+      <c r="G17" s="7">
+        <v>1.36</v>
+      </c>
+      <c r="H17" s="8">
+        <v>0.42</v>
+      </c>
+      <c r="I17" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="J17" s="7">
+        <v>26.1</v>
+      </c>
+      <c r="K17" s="8">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="L17" s="7">
+        <v>7.81</v>
+      </c>
+      <c r="M17" s="8">
+        <v>0.42</v>
+      </c>
+      <c r="N17" s="7">
+        <v>13.6</v>
+      </c>
+      <c r="O17" s="7">
+        <v>26.1</v>
+      </c>
+      <c r="P17" s="8">
+        <v>4.3499999999999996</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>7.81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" s="9" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10">
         <v>45597</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B18" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C18" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D18" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E18" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F17" s="8" t="s">
+      <c r="F18" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="8" t="s">
+      <c r="G18" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="H17" s="8">
+      <c r="H18" s="13">
         <v>0.37</v>
       </c>
-      <c r="I17" s="8" t="s">
+      <c r="I18" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J17" s="7">
+      <c r="J18" s="12">
         <v>12.6</v>
       </c>
-      <c r="K17" s="8">
+      <c r="K18" s="13">
         <v>3.93</v>
       </c>
-      <c r="L17" s="7">
+      <c r="L18" s="12">
         <v>6.16</v>
       </c>
-      <c r="M17" s="8">
+      <c r="M18" s="13">
         <v>0.37</v>
       </c>
-      <c r="N17" s="8" t="s">
+      <c r="N18" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="O17" s="7">
+      <c r="O18" s="12">
         <v>12.6</v>
       </c>
-      <c r="P17" s="8">
+      <c r="P18" s="13">
         <v>3.93</v>
       </c>
-      <c r="Q17" s="7">
+      <c r="Q18" s="12">
         <v>6.16</v>
       </c>
     </row>
